--- a/src/assets/downloads/Latvia-TestScenario4-AnnualProgressReport2026.xlsx
+++ b/src/assets/downloads/Latvia-TestScenario4-AnnualProgressReport2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ef7a825b9bce984a/Documents/Claude/Projects/FISCO/fisco-site/src/assets/downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="173" documentId="8_{5FF61014-9E2A-4B3F-B017-79FAC56A8DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F3603E3-8D2C-409D-8811-AE363C021007}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F60767A-6959-4A5A-9FAD-FEF0F802D58B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-67320" yWindow="-3945" windowWidth="29040" windowHeight="15720" xr2:uid="{8FD35C3B-BB10-4593-87EA-7C211D5C60DD}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{8FD35C3B-BB10-4593-87EA-7C211D5C60DD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2283,16 +2283,16 @@
         <v>1</v>
       </c>
       <c r="E56" s="15">
-        <v>2.9976595002552808</v>
+        <v>2.5</v>
       </c>
       <c r="F56" s="15">
-        <v>3.1420657625767783</v>
+        <v>2.6</v>
       </c>
       <c r="G56" s="15">
-        <v>3.4555754586740171</v>
+        <v>3</v>
       </c>
       <c r="H56" s="15">
-        <v>4.7257681343411875</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I56" s="15"/>
     </row>
